--- a/생활속의통계/Excel/3주차 실습데이터 0914.xlsx
+++ b/생활속의통계/Excel/3주차 실습데이터 0914.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545DCDB1-AC26-4461-A06F-D0CCA2EEC2C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8521F049-9413-4939-BD55-F59D281A5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="예제1" sheetId="4" r:id="rId1"/>
@@ -29,9 +29,9 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">예제2!$A$1:$A$10</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">실습3!$A$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">실습4!$B$1:$B$20</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">실습4!$A$1:$A$20</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">실습4!$B$1:$B$20</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">실습3!$B$2:$B$12</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">실습3!$A$2:$A$12</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">실습3!$B$2:$B$12</definedName>
     <definedName name="_xlchart.v1.13" hidden="1">실습4!$A$1:$A$20</definedName>
     <definedName name="_xlchart.v1.14" hidden="1">실습4!$B$1:$B$20</definedName>
     <definedName name="_xlchart.v1.15" hidden="1">'(참고)예제2답안'!$A$1:$A$10</definedName>
@@ -44,11 +44,11 @@
     <definedName name="_xlchart.v1.21" hidden="1">'(참고)실습4답안'!$B$1:$B$20</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">실습3!$B$1</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">실습3!$A$1</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">실습3!$A$2:$A$12</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">실습3!$B$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">실습3!$A$2:$A$12</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">실습3!$B$2:$B$12</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">실습3!$A$2:$A$12</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">실습4!$A$1:$A$20</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">실습3!$A$2:$A$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1135,6 +1135,59 @@
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.7</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.8</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000000-0D77-4A19-AF89-3AAAF67272D9}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{00000001-0D77-4A19-AF89-3AAAF67272D9}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
       <cx:strDim type="cat">
         <cx:f>_xlchart.v1.13</cx:f>
       </cx:strDim>
@@ -1169,7 +1222,7 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx5.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
@@ -1207,7 +1260,7 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx6.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
@@ -1273,7 +1326,7 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx7.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
@@ -1555,6 +1608,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
   <cs:axisTitle>
@@ -4645,20 +4738,535 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>216693</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>204787</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>311943</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>673893</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>83343</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -4694,8 +5302,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4331493" y="1276350"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="3055143" y="176212"/>
+              <a:ext cx="4572000" cy="2681288"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4777,7 +5385,85 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4331493" y="1276350"/>
+              <a:off x="4331493" y="1252537"/>
+              <a:ext cx="4572000" cy="2681288"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
+                <a:t>Excel 버전에서는 이 차트를 사용할 수 없습니다.
+이 도형 편집하거나 이 통합 문서를 다른 파일 형식으로 저장하면 차트가 영구적으로 손상됩니다.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="차트 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E99BC11C-BCB9-FFDE-3AE5-4A5BCAADD387}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="428625" y="3324225"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4860,8 +5546,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4331493" y="1276350"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="4331493" y="1252537"/>
+              <a:ext cx="4572000" cy="2681288"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4943,8 +5629,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3139440" y="0"/>
-              <a:ext cx="5505450" cy="3325178"/>
+              <a:off x="3158490" y="0"/>
+              <a:ext cx="5543550" cy="3253740"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5026,8 +5712,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2551748" y="0"/>
-              <a:ext cx="5735002" cy="3486150"/>
+              <a:off x="2566035" y="0"/>
+              <a:ext cx="5777865" cy="3409950"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5109,8 +5795,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3200400" y="0"/>
-              <a:ext cx="4578668" cy="2663190"/>
+              <a:off x="3219450" y="0"/>
+              <a:ext cx="4612005" cy="2606040"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5431,7 +6117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="5" max="5" width="14.375" customWidth="1"/>
@@ -5439,7 +6125,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>50</v>
       </c>
@@ -5447,12 +6133,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>36</v>
       </c>
@@ -5466,7 +6152,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>40</v>
       </c>
@@ -5479,7 +6165,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45</v>
       </c>
@@ -5492,177 +6178,177 @@
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>80</v>
       </c>
@@ -5677,9 +6363,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C119E0B-2CD1-4C38-B91B-4B69AFF7B8EC}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>71</v>
       </c>
@@ -5691,7 +6377,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>81</v>
       </c>
@@ -5703,7 +6389,7 @@
         <v>59.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>58</v>
       </c>
@@ -5715,7 +6401,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>60</v>
       </c>
@@ -5727,7 +6413,7 @@
         <v>69.75</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>63</v>
       </c>
@@ -5739,7 +6425,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>59</v>
       </c>
@@ -5751,22 +6437,22 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>45</v>
       </c>
@@ -5781,9 +6467,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3018850E-408F-4A22-A5F3-8F89AD7AAC11}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -5791,7 +6477,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>71</v>
       </c>
@@ -5799,7 +6485,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>81</v>
       </c>
@@ -5807,7 +6493,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>59</v>
       </c>
@@ -5815,7 +6501,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>60</v>
       </c>
@@ -5823,7 +6509,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>63</v>
       </c>
@@ -5831,7 +6517,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>76</v>
       </c>
@@ -5839,7 +6525,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>58</v>
       </c>
@@ -5847,7 +6533,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>69</v>
       </c>
@@ -5855,7 +6541,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>62</v>
       </c>
@@ -5863,12 +6549,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>31</v>
       </c>
@@ -5883,9 +6569,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B95554-F375-4E3F-AEA8-DD08BA50EA03}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -5893,7 +6579,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -5901,7 +6587,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>181</v>
       </c>
@@ -5909,7 +6595,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -5917,7 +6603,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -5925,7 +6611,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>182</v>
       </c>
@@ -5933,7 +6619,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>181</v>
       </c>
@@ -5941,7 +6627,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -5949,7 +6635,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>181</v>
       </c>
@@ -5957,7 +6643,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>182</v>
       </c>
@@ -5965,7 +6651,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>181</v>
       </c>
@@ -5973,7 +6659,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>182</v>
       </c>
@@ -5981,7 +6667,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>181</v>
       </c>
@@ -5989,7 +6675,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>182</v>
       </c>
@@ -5997,7 +6683,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>181</v>
       </c>
@@ -6005,7 +6691,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -6013,7 +6699,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -6021,7 +6707,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>182</v>
       </c>
@@ -6029,7 +6715,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -6037,7 +6723,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>181</v>
       </c>
@@ -6055,13 +6741,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J44"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="10.6875" customWidth="1"/>
+    <col min="8" max="11" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>183</v>
       </c>
@@ -6072,7 +6758,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6081,7 +6767,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -6090,7 +6776,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -6100,7 +6786,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -6127,7 +6813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -6158,7 +6844,7 @@
         <v>114756.75675675676</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -6189,7 +6875,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -6209,7 +6895,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -6229,7 +6915,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -6249,7 +6935,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -6269,7 +6955,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -6289,7 +6975,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>37</v>
       </c>
@@ -6309,7 +6995,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>40</v>
       </c>
@@ -6329,7 +7015,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -6349,7 +7035,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
@@ -6369,7 +7055,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -6389,7 +7075,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
@@ -6409,7 +7095,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
@@ -6429,7 +7115,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>54</v>
       </c>
@@ -6449,7 +7135,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
@@ -6469,7 +7155,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
@@ -6489,7 +7175,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -6509,7 +7195,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
@@ -6529,7 +7215,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -6549,7 +7235,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -6569,7 +7255,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>29</v>
       </c>
@@ -6589,7 +7275,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>79</v>
       </c>
@@ -6609,7 +7295,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
@@ -6629,7 +7315,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>84</v>
       </c>
@@ -6649,7 +7335,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>85</v>
       </c>
@@ -6669,7 +7355,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
@@ -6689,7 +7375,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -6709,7 +7395,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>92</v>
       </c>
@@ -6729,7 +7415,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>94</v>
       </c>
@@ -6749,7 +7435,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>95</v>
       </c>
@@ -6769,7 +7455,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>97</v>
       </c>
@@ -6789,7 +7475,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>100</v>
       </c>
@@ -6809,7 +7495,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>103</v>
       </c>
@@ -6829,7 +7515,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>104</v>
       </c>
@@ -6849,7 +7535,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>106</v>
       </c>
@@ -6869,7 +7555,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>109</v>
       </c>
@@ -6902,14 +7588,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.375" customWidth="1"/>
     <col min="9" max="9" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>190</v>
       </c>
@@ -6920,7 +7606,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6929,7 +7615,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -6938,7 +7624,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -6948,7 +7634,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>112</v>
       </c>
@@ -6975,7 +7661,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>118</v>
       </c>
@@ -7006,7 +7692,7 @@
         <v>31200</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>122</v>
       </c>
@@ -7037,7 +7723,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>126</v>
       </c>
@@ -7057,7 +7743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>130</v>
       </c>
@@ -7077,7 +7763,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>133</v>
       </c>
@@ -7097,7 +7783,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>135</v>
       </c>
@@ -7117,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>137</v>
       </c>
@@ -7137,7 +7823,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>139</v>
       </c>
@@ -7157,7 +7843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>142</v>
       </c>
@@ -7177,7 +7863,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>145</v>
       </c>
@@ -7197,7 +7883,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>146</v>
       </c>
@@ -7217,7 +7903,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>148</v>
       </c>
@@ -7237,7 +7923,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>150</v>
       </c>
@@ -7257,7 +7943,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>151</v>
       </c>
@@ -7277,7 +7963,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>152</v>
       </c>
@@ -7297,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>153</v>
       </c>
@@ -7317,7 +8003,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>154</v>
       </c>
@@ -7337,7 +8023,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>158</v>
       </c>
@@ -7357,7 +8043,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>159</v>
       </c>
@@ -7377,7 +8063,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>162</v>
       </c>
@@ -7397,7 +8083,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>163</v>
       </c>
@@ -7417,7 +8103,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>164</v>
       </c>
@@ -7437,7 +8123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>166</v>
       </c>
@@ -7457,7 +8143,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>169</v>
       </c>
@@ -7477,7 +8163,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>171</v>
       </c>
@@ -7510,9 +8196,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736EA0D5-CE47-4851-A7F7-61225BF175BD}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>71</v>
       </c>
@@ -7524,7 +8210,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>81</v>
       </c>
@@ -7536,7 +8222,7 @@
         <v>59.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>58</v>
       </c>
@@ -7548,7 +8234,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>60</v>
       </c>
@@ -7560,7 +8246,7 @@
         <v>69.75</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>63</v>
       </c>
@@ -7572,7 +8258,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>59</v>
       </c>
@@ -7584,22 +8270,22 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>45</v>
       </c>
@@ -7614,9 +8300,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE356186-AAFE-40A0-9C20-8C4E798BD36A}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -7630,7 +8316,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>71</v>
       </c>
@@ -7649,7 +8335,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>81</v>
       </c>
@@ -7668,7 +8354,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>59</v>
       </c>
@@ -7687,7 +8373,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>60</v>
       </c>
@@ -7706,7 +8392,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>63</v>
       </c>
@@ -7725,7 +8411,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>76</v>
       </c>
@@ -7744,7 +8430,7 @@
         <v>60.555555555555557</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>58</v>
       </c>
@@ -7752,7 +8438,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>69</v>
       </c>
@@ -7760,7 +8446,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>62</v>
       </c>
@@ -7768,12 +8454,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>31</v>
       </c>
@@ -7788,9 +8474,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B976803-A376-4236-895D-2226EC2A409A}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -7798,7 +8484,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -7806,7 +8492,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>181</v>
       </c>
@@ -7814,7 +8500,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -7822,7 +8508,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -7830,7 +8516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>182</v>
       </c>
@@ -7838,7 +8524,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>181</v>
       </c>
@@ -7846,7 +8532,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -7854,7 +8540,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>181</v>
       </c>
@@ -7862,7 +8548,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>182</v>
       </c>
@@ -7870,7 +8556,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>181</v>
       </c>
@@ -7878,7 +8564,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>182</v>
       </c>
@@ -7886,7 +8572,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>181</v>
       </c>
@@ -7894,7 +8580,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>182</v>
       </c>
@@ -7902,7 +8588,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>181</v>
       </c>
@@ -7910,7 +8596,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -7918,7 +8604,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -7926,7 +8612,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>182</v>
       </c>
@@ -7934,7 +8620,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -7942,7 +8628,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>181</v>
       </c>
@@ -7960,13 +8646,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E65998FE-ED8C-4324-89AC-D40083384FD5}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>50</v>
       </c>
@@ -7974,12 +8660,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>36</v>
       </c>
@@ -7993,7 +8679,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>40</v>
       </c>
@@ -8006,7 +8692,7 @@
       </c>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45</v>
       </c>
@@ -8019,7 +8705,7 @@
       </c>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>60</v>
       </c>
@@ -8032,175 +8718,175 @@
       </c>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>76</v>
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>40</v>
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>30</v>
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>80</v>
       </c>
@@ -8215,15 +8901,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2278200-495A-49C4-8225-A78EDEF21524}">
   <dimension ref="A1:J44"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="10" max="10" width="11.0625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>188</v>
       </c>
@@ -8234,7 +8920,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -8243,7 +8929,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -8252,7 +8938,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -8262,7 +8948,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -8289,7 +8975,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -8320,7 +9006,7 @@
         <v>376000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -8351,7 +9037,7 @@
         <v>8103244744.7447443</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -8382,7 +9068,7 @@
         <v>90018.02455477872</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -8402,7 +9088,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -8422,7 +9108,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -8442,7 +9128,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -8462,7 +9148,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>37</v>
       </c>
@@ -8482,7 +9168,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>40</v>
       </c>
@@ -8502,7 +9188,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -8522,7 +9208,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
@@ -8542,7 +9228,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -8562,7 +9248,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
@@ -8582,7 +9268,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
@@ -8602,7 +9288,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>54</v>
       </c>
@@ -8622,7 +9308,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
@@ -8642,7 +9328,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
@@ -8662,7 +9348,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -8682,7 +9368,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
@@ -8702,7 +9388,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -8722,7 +9408,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -8742,7 +9428,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>29</v>
       </c>
@@ -8762,7 +9448,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>79</v>
       </c>
@@ -8782,7 +9468,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
@@ -8802,7 +9488,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>84</v>
       </c>
@@ -8822,7 +9508,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>85</v>
       </c>
@@ -8842,7 +9528,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
@@ -8862,7 +9548,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -8882,7 +9568,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>92</v>
       </c>
@@ -8902,7 +9588,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>94</v>
       </c>
@@ -8922,7 +9608,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>95</v>
       </c>
@@ -8942,7 +9628,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>97</v>
       </c>
@@ -8962,7 +9648,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>100</v>
       </c>
@@ -8982,7 +9668,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>103</v>
       </c>
@@ -9002,7 +9688,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>104</v>
       </c>
@@ -9022,7 +9708,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>106</v>
       </c>
@@ -9042,7 +9728,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>109</v>
       </c>
@@ -9075,18 +9761,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A642227C-EFBB-4BC5-AC84-A6510B50B1E2}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.375" customWidth="1"/>
-    <col min="8" max="8" width="12.6875" customWidth="1"/>
-    <col min="9" max="9" width="16.1875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+    <col min="9" max="9" width="16.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.625" customWidth="1"/>
     <col min="11" max="11" width="14.125" customWidth="1"/>
     <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>189</v>
       </c>
@@ -9097,7 +9783,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -9106,7 +9792,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -9115,7 +9801,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -9125,7 +9811,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
         <v>116</v>
@@ -9134,7 +9820,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -9165,7 +9851,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>118</v>
       </c>
@@ -9196,7 +9882,7 @@
         <v>486000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>122</v>
       </c>
@@ -9228,7 +9914,7 @@
       </c>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
@@ -9249,7 +9935,7 @@
       </c>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>130</v>
       </c>
@@ -9270,7 +9956,7 @@
       </c>
       <c r="I12" s="13"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>133</v>
       </c>
@@ -9291,7 +9977,7 @@
       </c>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>135</v>
       </c>
@@ -9312,7 +9998,7 @@
       </c>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>137</v>
       </c>
@@ -9333,7 +10019,7 @@
       </c>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>139</v>
       </c>
@@ -9353,7 +10039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>142</v>
       </c>
@@ -9375,7 +10061,7 @@
       <c r="I17" s="13"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>145</v>
       </c>
@@ -9395,7 +10081,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>146</v>
       </c>
@@ -9417,7 +10103,7 @@
       <c r="I19" s="13"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>148</v>
       </c>
@@ -9438,7 +10124,7 @@
       </c>
       <c r="I20" s="13"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>150</v>
       </c>
@@ -9459,7 +10145,7 @@
       </c>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>151</v>
       </c>
@@ -9480,7 +10166,7 @@
       </c>
       <c r="I22" s="13"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>152</v>
       </c>
@@ -9501,7 +10187,7 @@
       </c>
       <c r="I23" s="13"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>153</v>
       </c>
@@ -9522,7 +10208,7 @@
       </c>
       <c r="I24" s="13"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>154</v>
       </c>
@@ -9542,7 +10228,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>158</v>
       </c>
@@ -9562,7 +10248,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>159</v>
       </c>
@@ -9582,7 +10268,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>162</v>
       </c>
@@ -9602,7 +10288,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>163</v>
       </c>
@@ -9622,7 +10308,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>164</v>
       </c>
@@ -9642,7 +10328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>166</v>
       </c>
@@ -9662,7 +10348,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>169</v>
       </c>
@@ -9682,7 +10368,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>171</v>
       </c>

--- a/생활속의통계/Excel/3주차 실습데이터 0914.xlsx
+++ b/생활속의통계/Excel/3주차 실습데이터 0914.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KBS\Desktop\hayeun\26_2_myLecture\생활속의통계\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8521F049-9413-4939-BD55-F59D281A5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6864FF-356D-4F34-8A66-989D0E9D9D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="예제1" sheetId="4" r:id="rId1"/>
@@ -28,27 +28,26 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">예제2!$A$1:$A$10</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">실습3!$A$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">실습3!$A$2:$A$12</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">실습4!$A$1:$A$20</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">실습4!$B$1:$B$20</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'(참고)예제2답안'!$A$1:$A$10</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'(참고)실습3답안'!$A$1</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'(참고)실습3답안'!$A$2:$A$12</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'(참고)실습3답안'!$B$1</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'(참고)실습3답안'!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">실습3!$A$2:$A$12</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'(참고)실습4답안'!$A$1:$A$20</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'(참고)실습4답안'!$B$1:$B$20</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">실습3!$B$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">실습3!$A$2:$A$12</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">실습3!$A$2:$A$12</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">실습3!$B$2:$B$12</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">실습3!$A$2:$A$12</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">예제2!$A$1:$A$10</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">실습4!$A$1:$A$20</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">실습4!$B$1:$B$20</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">실습4!$A$1:$A$20</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">실습4!$B$1:$B$20</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'(참고)예제2답안'!$A$1:$A$10</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'(참고)실습3답안'!$A$1</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'(참고)실습3답안'!$A$2:$A$12</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'(참고)실습3답안'!$B$1</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'(참고)실습3답안'!$B$2:$B$12</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'(참고)실습4답안'!$A$1:$A$20</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">실습3!$A$1</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">'(참고)실습4답안'!$B$1:$B$20</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">실습3!$A$2:$A$12</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">실습3!$B$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">실습3!$B$2:$B$12</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">실습3!$A$2:$A$12</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">실습3!$B$2:$B$12</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">실습4!$A$1:$A$20</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">실습4!$B$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1033,7 +1032,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1041,7 +1040,7 @@
     <cx:title pos="t" align="ctr" overlay="0"/>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{00000000-51A4-4725-BDF7-CE6889E82923}">
+        <cx:series layoutId="boxWhisker" uniqueId="{00000000-7C4B-4845-9F37-04791A342BD4}">
           <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
@@ -1071,12 +1070,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.4</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1087,7 +1086,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000000-13E5-41FE-956C-2C9B7A2984A3}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Group 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1103,7 +1102,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{00000001-13E5-41FE-956C-2C9B7A2984A3}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Group 2</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1136,12 +1135,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.8</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1189,10 +1188,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.13</cx:f>
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.14</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1201,6 +1200,9 @@
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="boxWhisker" uniqueId="{00000000-9164-4E7B-B775-F2AA66E32832}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1227,7 +1229,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.15</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1265,12 +1267,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.17</cx:f>
+        <cx:f>_xlchart.v1.16</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.19</cx:f>
+        <cx:f>_xlchart.v1.18</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1281,7 +1283,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{7EABB7CF-5978-42BC-BF41-7B3568A26141}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.16</cx:f>
+              <cx:f>_xlchart.v1.15</cx:f>
               <cx:v>Group 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1297,7 +1299,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{B1B4E5FB-D293-46D2-99F1-7AF3C4A53DAB}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.18</cx:f>
+              <cx:f>_xlchart.v1.17</cx:f>
               <cx:v>Group 2</cx:v>
             </cx:txData>
           </cx:tx>
@@ -1331,10 +1333,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.20</cx:f>
+        <cx:f>_xlchart.v1.19</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.21</cx:f>
+        <cx:f>_xlchart.v1.20</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -5257,25 +5259,25 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>311943</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>645318</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>83343</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>416718</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="차트 3">
+            <xdr:cNvPr id="2" name="차트 1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4018DC4-E36D-8A71-417D-909D9C6E2813}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A540D1F-8951-0042-72D8-A8FBEBE67ED7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -5302,8 +5304,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3055143" y="176212"/>
-              <a:ext cx="4572000" cy="2681288"/>
+              <a:off x="4074318" y="762000"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5385,8 +5387,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4331493" y="1252537"/>
-              <a:ext cx="4572000" cy="2681288"/>
+              <a:off x="4331493" y="1276350"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5463,8 +5465,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="428625" y="3324225"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="428625" y="3395663"/>
+              <a:ext cx="4572000" cy="2805112"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5546,8 +5548,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4331493" y="1252537"/>
-              <a:ext cx="4572000" cy="2681288"/>
+              <a:off x="4331493" y="1276350"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5630,7 +5632,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="3158490" y="0"/>
-              <a:ext cx="5543550" cy="3253740"/>
+              <a:ext cx="5543550" cy="3325178"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5713,7 +5715,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="2566035" y="0"/>
-              <a:ext cx="5777865" cy="3409950"/>
+              <a:ext cx="5777865" cy="3486150"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -5796,7 +5798,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="3219450" y="0"/>
-              <a:ext cx="4612005" cy="2606040"/>
+              <a:ext cx="4612005" cy="2663190"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6117,7 +6119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="5" max="5" width="14.375" customWidth="1"/>
@@ -6125,7 +6127,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A1" s="1">
         <v>50</v>
       </c>
@@ -6133,12 +6135,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A2" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A3" s="1">
         <v>36</v>
       </c>
@@ -6152,7 +6154,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A4" s="1">
         <v>40</v>
       </c>
@@ -6165,7 +6167,7 @@
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A5" s="1">
         <v>45</v>
       </c>
@@ -6178,177 +6180,177 @@
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A7" s="1">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A9" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A10" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A13" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A14" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A15" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.6">
       <c r="A16" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A17" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A18" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A19" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A20" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A21" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A22" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A23" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A24" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A25" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A26" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A27" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A28" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A29" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A30" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A31" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A32" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A33" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A34" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A35" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A36" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A37" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A38" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A40" s="1">
         <v>80</v>
       </c>
@@ -6363,9 +6365,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C119E0B-2CD1-4C38-B91B-4B69AFF7B8EC}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A1">
         <v>71</v>
       </c>
@@ -6377,7 +6379,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>81</v>
       </c>
@@ -6389,7 +6391,7 @@
         <v>59.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>58</v>
       </c>
@@ -6401,7 +6403,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>60</v>
       </c>
@@ -6413,7 +6415,7 @@
         <v>69.75</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>63</v>
       </c>
@@ -6425,7 +6427,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>59</v>
       </c>
@@ -6437,22 +6439,22 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>45</v>
       </c>
@@ -6467,9 +6469,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3018850E-408F-4A22-A5F3-8F89AD7AAC11}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -6477,7 +6479,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>71</v>
       </c>
@@ -6485,7 +6487,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>81</v>
       </c>
@@ -6493,7 +6495,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>59</v>
       </c>
@@ -6501,7 +6503,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>60</v>
       </c>
@@ -6509,7 +6511,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>63</v>
       </c>
@@ -6517,7 +6519,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>76</v>
       </c>
@@ -6525,7 +6527,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>58</v>
       </c>
@@ -6533,7 +6535,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>69</v>
       </c>
@@ -6541,7 +6543,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>62</v>
       </c>
@@ -6549,12 +6551,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>31</v>
       </c>
@@ -6569,9 +6571,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B95554-F375-4E3F-AEA8-DD08BA50EA03}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -6579,7 +6581,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -6587,7 +6589,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>181</v>
       </c>
@@ -6595,7 +6597,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -6603,7 +6605,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -6611,7 +6613,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>182</v>
       </c>
@@ -6619,7 +6621,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>181</v>
       </c>
@@ -6627,7 +6629,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -6635,7 +6637,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>181</v>
       </c>
@@ -6643,7 +6645,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>182</v>
       </c>
@@ -6651,7 +6653,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>181</v>
       </c>
@@ -6659,7 +6661,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>182</v>
       </c>
@@ -6667,7 +6669,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>181</v>
       </c>
@@ -6675,7 +6677,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>182</v>
       </c>
@@ -6683,7 +6685,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>181</v>
       </c>
@@ -6691,7 +6693,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -6699,7 +6701,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -6707,7 +6709,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>182</v>
       </c>
@@ -6715,7 +6717,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -6723,7 +6725,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A20" t="s">
         <v>181</v>
       </c>
@@ -6741,13 +6743,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
     <col min="8" max="11" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" s="17" t="s">
         <v>183</v>
       </c>
@@ -6758,7 +6760,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -6767,7 +6769,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -6776,7 +6778,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -6786,7 +6788,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -6813,7 +6815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -6844,7 +6846,7 @@
         <v>114756.75675675676</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -6875,7 +6877,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -6895,7 +6897,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -6915,7 +6917,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -6935,7 +6937,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -6955,7 +6957,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -6975,7 +6977,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" s="8" t="s">
         <v>37</v>
       </c>
@@ -6995,7 +6997,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" s="8" t="s">
         <v>40</v>
       </c>
@@ -7015,7 +7017,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -7035,7 +7037,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
@@ -7055,7 +7057,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -7075,7 +7077,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
@@ -7095,7 +7097,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
@@ -7115,7 +7117,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
         <v>54</v>
       </c>
@@ -7135,7 +7137,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
@@ -7155,7 +7157,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
@@ -7175,7 +7177,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -7195,7 +7197,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
@@ -7215,7 +7217,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -7235,7 +7237,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -7255,7 +7257,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A29" s="7" t="s">
         <v>29</v>
       </c>
@@ -7275,7 +7277,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A30" s="7" t="s">
         <v>79</v>
       </c>
@@ -7295,7 +7297,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
@@ -7315,7 +7317,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A32" s="7" t="s">
         <v>84</v>
       </c>
@@ -7335,7 +7337,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A33" s="7" t="s">
         <v>85</v>
       </c>
@@ -7355,7 +7357,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
@@ -7375,7 +7377,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -7395,7 +7397,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A36" s="4" t="s">
         <v>92</v>
       </c>
@@ -7415,7 +7417,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A37" s="4" t="s">
         <v>94</v>
       </c>
@@ -7435,7 +7437,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A38" s="4" t="s">
         <v>95</v>
       </c>
@@ -7455,7 +7457,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A39" s="4" t="s">
         <v>97</v>
       </c>
@@ -7475,7 +7477,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A40" s="4" t="s">
         <v>100</v>
       </c>
@@ -7495,7 +7497,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A41" s="4" t="s">
         <v>103</v>
       </c>
@@ -7515,7 +7517,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A42" s="4" t="s">
         <v>104</v>
       </c>
@@ -7535,7 +7537,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A43" s="4" t="s">
         <v>106</v>
       </c>
@@ -7555,7 +7557,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A44" s="4" t="s">
         <v>109</v>
       </c>
@@ -7588,14 +7590,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.375" customWidth="1"/>
     <col min="9" max="9" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" s="17" t="s">
         <v>190</v>
       </c>
@@ -7606,7 +7608,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -7615,7 +7617,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -7624,7 +7626,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -7634,7 +7636,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7" s="3" t="s">
         <v>112</v>
       </c>
@@ -7661,7 +7663,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A8" s="4" t="s">
         <v>118</v>
       </c>
@@ -7692,7 +7694,7 @@
         <v>31200</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A9" s="4" t="s">
         <v>122</v>
       </c>
@@ -7723,7 +7725,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="4" t="s">
         <v>126</v>
       </c>
@@ -7743,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" s="7" t="s">
         <v>130</v>
       </c>
@@ -7763,7 +7765,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A12" s="8" t="s">
         <v>133</v>
       </c>
@@ -7783,7 +7785,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A13" s="4" t="s">
         <v>135</v>
       </c>
@@ -7803,7 +7805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
         <v>137</v>
       </c>
@@ -7823,7 +7825,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" s="7" t="s">
         <v>139</v>
       </c>
@@ -7843,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" s="4" t="s">
         <v>142</v>
       </c>
@@ -7863,7 +7865,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="8" t="s">
         <v>145</v>
       </c>
@@ -7883,7 +7885,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="8" t="s">
         <v>146</v>
       </c>
@@ -7903,7 +7905,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="7" t="s">
         <v>148</v>
       </c>
@@ -7923,7 +7925,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A20" s="8" t="s">
         <v>150</v>
       </c>
@@ -7943,7 +7945,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A21" s="4" t="s">
         <v>151</v>
       </c>
@@ -7963,7 +7965,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
         <v>152</v>
       </c>
@@ -7983,7 +7985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
         <v>153</v>
       </c>
@@ -8003,7 +8005,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
         <v>154</v>
       </c>
@@ -8023,7 +8025,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
         <v>158</v>
       </c>
@@ -8043,7 +8045,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
         <v>159</v>
       </c>
@@ -8063,7 +8065,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A27" s="7" t="s">
         <v>162</v>
       </c>
@@ -8083,7 +8085,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
         <v>163</v>
       </c>
@@ -8103,7 +8105,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A29" s="7" t="s">
         <v>164</v>
       </c>
@@ -8123,7 +8125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A30" s="7" t="s">
         <v>166</v>
       </c>
@@ -8143,7 +8145,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A31" s="7" t="s">
         <v>169</v>
       </c>
@@ -8163,7 +8165,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A32" s="7" t="s">
         <v>171</v>
       </c>
@@ -8196,9 +8198,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736EA0D5-CE47-4851-A7F7-61225BF175BD}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A1">
         <v>71</v>
       </c>
@@ -8210,7 +8212,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>81</v>
       </c>
@@ -8218,11 +8220,11 @@
         <v>185</v>
       </c>
       <c r="D2">
-        <f>QUARTILE(A1:A10,1)</f>
+        <f>QUARTILE(A1:A10, 1)</f>
         <v>59.25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>58</v>
       </c>
@@ -8234,7 +8236,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>60</v>
       </c>
@@ -8246,7 +8248,7 @@
         <v>69.75</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>63</v>
       </c>
@@ -8258,7 +8260,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>59</v>
       </c>
@@ -8270,22 +8272,22 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>45</v>
       </c>
@@ -8300,9 +8302,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE356186-AAFE-40A0-9C20-8C4E798BD36A}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -8316,7 +8318,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>71</v>
       </c>
@@ -8335,7 +8337,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>81</v>
       </c>
@@ -8354,7 +8356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>59</v>
       </c>
@@ -8373,7 +8375,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>60</v>
       </c>
@@ -8392,7 +8394,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>63</v>
       </c>
@@ -8411,7 +8413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>76</v>
       </c>
@@ -8430,7 +8432,7 @@
         <v>60.555555555555557</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>58</v>
       </c>
@@ -8438,7 +8440,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>69</v>
       </c>
@@ -8446,7 +8448,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>62</v>
       </c>
@@ -8454,12 +8456,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>31</v>
       </c>
@@ -8474,9 +8476,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B976803-A376-4236-895D-2226EC2A409A}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>181</v>
       </c>
@@ -8484,7 +8486,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -8492,7 +8494,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>181</v>
       </c>
@@ -8500,7 +8502,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>182</v>
       </c>
@@ -8508,7 +8510,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -8516,7 +8518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>182</v>
       </c>
@@ -8524,7 +8526,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>181</v>
       </c>
@@ -8532,7 +8534,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>182</v>
       </c>
@@ -8540,7 +8542,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>181</v>
       </c>
@@ -8548,7 +8550,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>182</v>
       </c>
@@ -8556,7 +8558,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>181</v>
       </c>
@@ -8564,7 +8566,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>182</v>
       </c>
@@ -8572,7 +8574,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>181</v>
       </c>
@@ -8580,7 +8582,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>182</v>
       </c>
@@ -8588,7 +8590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>181</v>
       </c>
@@ -8596,7 +8598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>182</v>
       </c>
@@ -8604,7 +8606,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>181</v>
       </c>
@@ -8612,7 +8614,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>182</v>
       </c>
@@ -8620,7 +8622,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -8628,7 +8630,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A20" t="s">
         <v>181</v>
       </c>
@@ -8646,13 +8648,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E65998FE-ED8C-4324-89AC-D40083384FD5}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A1" s="1">
         <v>50</v>
       </c>
@@ -8660,12 +8662,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A2" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A3" s="1">
         <v>36</v>
       </c>
@@ -8679,7 +8681,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A4" s="1">
         <v>40</v>
       </c>
@@ -8692,7 +8694,7 @@
       </c>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A5" s="1">
         <v>45</v>
       </c>
@@ -8705,7 +8707,7 @@
       </c>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>60</v>
       </c>
@@ -8718,175 +8720,175 @@
       </c>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A7" s="1">
         <v>76</v>
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A9" s="1">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A10" s="1">
         <v>40</v>
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
         <v>30</v>
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A13" s="1">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A14" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A15" s="1">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.6">
       <c r="A16" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A17" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A18" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A19" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A20" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A21" s="1">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A22" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A23" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A24" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A25" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A26" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A27" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A28" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A29" s="1">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A30" s="1">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A31" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A32" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A33" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A34" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A35" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A36" s="1">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A37" s="1">
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A38" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.6">
       <c r="A40" s="1">
         <v>80</v>
       </c>
@@ -8901,7 +8903,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2278200-495A-49C4-8225-A78EDEF21524}">
   <dimension ref="A1:J44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="6" max="6" width="9.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
@@ -8909,7 +8911,7 @@
     <col min="11" max="11" width="9.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" s="17" t="s">
         <v>188</v>
       </c>
@@ -8920,7 +8922,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -8929,7 +8931,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -8938,7 +8940,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -8948,7 +8950,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -8975,7 +8977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
@@ -9006,7 +9008,7 @@
         <v>376000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -9037,7 +9039,7 @@
         <v>8103244744.7447443</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A10" s="7" t="s">
         <v>19</v>
       </c>
@@ -9068,7 +9070,7 @@
         <v>90018.02455477872</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
         <v>23</v>
       </c>
@@ -9088,7 +9090,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
@@ -9108,7 +9110,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -9128,7 +9130,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
@@ -9148,7 +9150,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A15" s="8" t="s">
         <v>37</v>
       </c>
@@ -9168,7 +9170,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A16" s="8" t="s">
         <v>40</v>
       </c>
@@ -9188,7 +9190,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A17" s="8" t="s">
         <v>44</v>
       </c>
@@ -9208,7 +9210,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
@@ -9228,7 +9230,7 @@
         <v>95000</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
@@ -9248,7 +9250,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
@@ -9268,7 +9270,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
@@ -9288,7 +9290,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
         <v>54</v>
       </c>
@@ -9308,7 +9310,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
@@ -9328,7 +9330,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
@@ -9348,7 +9350,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -9368,7 +9370,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
@@ -9388,7 +9390,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A27" s="4" t="s">
         <v>70</v>
       </c>
@@ -9408,7 +9410,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -9428,7 +9430,7 @@
         <v>171000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A29" s="7" t="s">
         <v>29</v>
       </c>
@@ -9448,7 +9450,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A30" s="7" t="s">
         <v>79</v>
       </c>
@@ -9468,7 +9470,7 @@
         <v>83000</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
@@ -9488,7 +9490,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A32" s="7" t="s">
         <v>84</v>
       </c>
@@ -9508,7 +9510,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A33" s="7" t="s">
         <v>85</v>
       </c>
@@ -9528,7 +9530,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A34" s="4" t="s">
         <v>88</v>
       </c>
@@ -9548,7 +9550,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A35" s="4" t="s">
         <v>90</v>
       </c>
@@ -9568,7 +9570,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A36" s="4" t="s">
         <v>92</v>
       </c>
@@ -9588,7 +9590,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A37" s="4" t="s">
         <v>94</v>
       </c>
@@ -9608,7 +9610,7 @@
         <v>215000</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A38" s="4" t="s">
         <v>95</v>
       </c>
@@ -9628,7 +9630,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A39" s="4" t="s">
         <v>97</v>
       </c>
@@ -9648,7 +9650,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A40" s="4" t="s">
         <v>100</v>
       </c>
@@ -9668,7 +9670,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A41" s="4" t="s">
         <v>103</v>
       </c>
@@ -9688,7 +9690,7 @@
         <v>63000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A42" s="4" t="s">
         <v>104</v>
       </c>
@@ -9708,7 +9710,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A43" s="4" t="s">
         <v>106</v>
       </c>
@@ -9728,7 +9730,7 @@
         <v>211000</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A44" s="4" t="s">
         <v>109</v>
       </c>
@@ -9761,7 +9763,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A642227C-EFBB-4BC5-AC84-A6510B50B1E2}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.375" customWidth="1"/>
@@ -9772,7 +9774,7 @@
     <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A1" s="17" t="s">
         <v>189</v>
       </c>
@@ -9783,7 +9785,7 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -9792,7 +9794,7 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -9801,7 +9803,7 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -9811,7 +9813,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.6">
       <c r="H7" s="10"/>
       <c r="I7" s="10" t="s">
         <v>116</v>
@@ -9820,7 +9822,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -9851,7 +9853,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A9" s="4" t="s">
         <v>118</v>
       </c>
@@ -9882,7 +9884,7 @@
         <v>486000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A10" s="4" t="s">
         <v>122</v>
       </c>
@@ -9914,7 +9916,7 @@
       </c>
       <c r="L10" s="14"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
@@ -9935,7 +9937,7 @@
       </c>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A12" s="7" t="s">
         <v>130</v>
       </c>
@@ -9956,7 +9958,7 @@
       </c>
       <c r="I12" s="13"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A13" s="8" t="s">
         <v>133</v>
       </c>
@@ -9977,7 +9979,7 @@
       </c>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
         <v>135</v>
       </c>
@@ -9998,7 +10000,7 @@
       </c>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
         <v>137</v>
       </c>
@@ -10019,7 +10021,7 @@
       </c>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A16" s="7" t="s">
         <v>139</v>
       </c>
@@ -10039,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A17" s="4" t="s">
         <v>142</v>
       </c>
@@ -10061,7 +10063,7 @@
       <c r="I17" s="13"/>
       <c r="K17" s="14"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A18" s="8" t="s">
         <v>145</v>
       </c>
@@ -10081,7 +10083,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A19" s="8" t="s">
         <v>146</v>
       </c>
@@ -10103,7 +10105,7 @@
       <c r="I19" s="13"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A20" s="7" t="s">
         <v>148</v>
       </c>
@@ -10124,7 +10126,7 @@
       </c>
       <c r="I20" s="13"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A21" s="8" t="s">
         <v>150</v>
       </c>
@@ -10145,7 +10147,7 @@
       </c>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
         <v>151</v>
       </c>
@@ -10166,7 +10168,7 @@
       </c>
       <c r="I22" s="13"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
         <v>152</v>
       </c>
@@ -10187,7 +10189,7 @@
       </c>
       <c r="I23" s="13"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
         <v>153</v>
       </c>
@@ -10208,7 +10210,7 @@
       </c>
       <c r="I24" s="13"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
         <v>154</v>
       </c>
@@ -10228,7 +10230,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
         <v>158</v>
       </c>
@@ -10248,7 +10250,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A27" s="4" t="s">
         <v>159</v>
       </c>
@@ -10268,7 +10270,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A28" s="7" t="s">
         <v>162</v>
       </c>
@@ -10288,7 +10290,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A29" s="4" t="s">
         <v>163</v>
       </c>
@@ -10308,7 +10310,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A30" s="7" t="s">
         <v>164</v>
       </c>
@@ -10328,7 +10330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A31" s="7" t="s">
         <v>166</v>
       </c>
@@ -10348,7 +10350,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A32" s="7" t="s">
         <v>169</v>
       </c>
@@ -10368,7 +10370,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A33" s="7" t="s">
         <v>171</v>
       </c>
